--- a/nilai-nilai/gti-2026/Penilaian_GTI_2026_FINAL.xlsx
+++ b/nilai-nilai/gti-2026/Penilaian_GTI_2026_FINAL.xlsx
@@ -1456,7 +1456,7 @@
         <v>8</v>
       </c>
       <c r="P6" s="39" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q6" s="39" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: E.</t>
+          <t>Skala 60-90 | video: A3 | raw→70→84</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="P7" s="39" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q7" s="39" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: E.</t>
+          <t>Skala 60-90 | video: A3 | raw→70→84</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="P8" s="39" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="39" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: E.</t>
+          <t>Skala 60-90 | video: A3 | raw→70→84</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
         <v>8</v>
       </c>
       <c r="P9" s="39" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="39" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: E.</t>
+          <t>Skala 60-90 | video: A3 | raw→70→84</t>
         </is>
       </c>
     </row>
@@ -1735,17 +1735,17 @@
       <c r="O10" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P10" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q10" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P10" s="41" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, D, I, J.</t>
+          <t>Skala 60-90 | video: A4 | raw→55→73</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
       <c r="O11" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P11" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q11" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P11" s="41" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q11" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, D, I, J.</t>
+          <t>Skala 60-90 | video: A4 | raw→55→73</t>
         </is>
       </c>
     </row>
@@ -1875,17 +1875,17 @@
       <c r="O12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P12" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q12" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P12" s="41" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, D, I, J.</t>
+          <t>Skala 60-90 | video: A4 | raw→55→73</t>
         </is>
       </c>
     </row>
@@ -1945,17 +1945,17 @@
       <c r="O13" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P13" s="39" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q13" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P13" s="42" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q13" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=81.</t>
+          <t>Skala 60-90 | video: A5 | raw→73→86</t>
         </is>
       </c>
     </row>
@@ -2015,17 +2015,17 @@
       <c r="O14" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P14" s="39" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q14" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P14" s="42" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q14" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=81.</t>
+          <t>Skala 60-90 | video: A5 | raw→73→86</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2085,17 @@
       <c r="O15" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P15" s="39" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q15" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P15" s="42" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q15" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=81.</t>
+          <t>Skala 60-90 | video: A5 | raw→73→86</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
       <c r="O16" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P16" s="39" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q16" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P16" s="42" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q16" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=81.</t>
+          <t>Skala 60-90 | video: A5 | raw→73→86</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
         <v>8</v>
       </c>
       <c r="P17" s="39" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q17" s="39" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=80.</t>
+          <t>Skala 60-90 | video: A6 | raw→70→84</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
         <v>8</v>
       </c>
       <c r="P18" s="39" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q18" s="39" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=80.</t>
+          <t>Skala 60-90 | video: A6 | raw→70→84</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="P19" s="39" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="39" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=80.</t>
+          <t>Skala 60-90 | video: A6 | raw→70→84</t>
         </is>
       </c>
     </row>
@@ -2435,17 +2435,17 @@
       <c r="O20" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P20" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q20" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P20" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=59. Komponen lemah: C, D, F, G, H, J. [min60: 59→60]</t>
+          <t>Skala 60-90 | video: A7 | raw→54→72</t>
         </is>
       </c>
     </row>
@@ -2505,17 +2505,17 @@
       <c r="O21" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P21" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q21" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P21" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=59. Komponen lemah: C, D, F, G, H, J. [min60: 59→60]</t>
+          <t>Skala 60-90 | video: A7 | raw→54→72</t>
         </is>
       </c>
     </row>
@@ -2575,17 +2575,17 @@
       <c r="O22" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q22" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P22" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q22" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=59. Komponen lemah: C, D, F, G, H, J. [min60: 59→60]</t>
+          <t>Skala 60-90 | video: A7 | raw→54→72</t>
         </is>
       </c>
     </row>
@@ -2645,17 +2645,17 @@
       <c r="O23" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q23" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P23" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q23" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=59. Komponen lemah: C, D, F, G, H, J. [min60: 59→60]</t>
+          <t>Skala 60-90 | video: A7 | raw→54→72</t>
         </is>
       </c>
     </row>
@@ -2715,17 +2715,17 @@
       <c r="O24" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="41" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q24" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P24" s="39" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q24" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=67. Komponen lemah: C, G, J.</t>
+          <t>Skala 60-90 | video: A8 | raw→60→77</t>
         </is>
       </c>
     </row>
@@ -2785,17 +2785,17 @@
       <c r="O25" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P25" s="41" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q25" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P25" s="39" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q25" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=67. Komponen lemah: C, G, J.</t>
+          <t>Skala 60-90 | video: A8 | raw→60→77</t>
         </is>
       </c>
     </row>
@@ -2855,17 +2855,17 @@
       <c r="O26" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P26" s="41" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q26" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P26" s="39" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q26" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=67. Komponen lemah: C, G, J.</t>
+          <t>Skala 60-90 | video: A8 | raw→60→77</t>
         </is>
       </c>
     </row>
@@ -2925,17 +2925,17 @@
       <c r="O27" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P27" s="41" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q27" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P27" s="39" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q27" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=67. Komponen lemah: C, G, J.</t>
+          <t>Skala 60-90 | video: A8 | raw→60→77</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       <c r="O28" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P28" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q28" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P28" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q28" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: H, I.</t>
+          <t>Skala 60-90 | video: A9 | raw→64→80</t>
         </is>
       </c>
     </row>
@@ -3065,17 +3065,17 @@
       <c r="O29" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P29" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q29" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P29" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q29" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: H, I.</t>
+          <t>Skala 60-90 | video: A9 | raw→64→80</t>
         </is>
       </c>
     </row>
@@ -3135,17 +3135,17 @@
       <c r="O30" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P30" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q30" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P30" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q30" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: H, I.</t>
+          <t>Skala 60-90 | video: A9 | raw→64→80</t>
         </is>
       </c>
     </row>
@@ -3205,17 +3205,17 @@
       <c r="O31" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P31" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q31" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P31" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q31" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: H, I.</t>
+          <t>Skala 60-90 | video: A9 | raw→64→80</t>
         </is>
       </c>
     </row>
@@ -3275,17 +3275,17 @@
       <c r="O32" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P32" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q32" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P32" s="41" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=49. Komponen lemah: C, D, E, F, G, H, I, J. [min60: 49→60]</t>
+          <t>Skala 60-90 | video: A10 | raw→48→68</t>
         </is>
       </c>
     </row>
@@ -3345,17 +3345,17 @@
       <c r="O33" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q33" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P33" s="41" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q33" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=49. Komponen lemah: C, D, E, F, G, H, I, J. [min60: 49→60]</t>
+          <t>Skala 60-90 | video: A10 | raw→48→68</t>
         </is>
       </c>
     </row>
@@ -3415,17 +3415,17 @@
       <c r="O34" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P34" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q34" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P34" s="41" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q34" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=49. Komponen lemah: C, D, E, F, G, H, I, J. [min60: 49→60]</t>
+          <t>Skala 60-90 | video: A10 | raw→48→68</t>
         </is>
       </c>
     </row>
@@ -3485,17 +3485,17 @@
       <c r="O35" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P35" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q35" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P35" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q35" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=48. Komponen lemah: B, C, D, E, F, H, I, J. [min60: 48→60]</t>
+          <t>Skala 60-90 | video: A11 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -3555,17 +3555,17 @@
       <c r="O36" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P36" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q36" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P36" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q36" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=48. Komponen lemah: B, C, D, E, F, H, I, J. [min60: 48→60]</t>
+          <t>Skala 60-90 | video: A11 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -3625,17 +3625,17 @@
       <c r="O37" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P37" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q37" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P37" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q37" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=48. Komponen lemah: B, C, D, E, F, H, I, J. [min60: 48→60]</t>
+          <t>Skala 60-90 | video: A11 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -3735,17 +3735,17 @@
       <c r="O39" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P39" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q39" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P39" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q39" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=46. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 46→60]</t>
+          <t>Skala 60-90 | video: A13 | raw→46→67</t>
         </is>
       </c>
     </row>
@@ -3805,17 +3805,17 @@
       <c r="O40" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P40" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q40" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P40" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q40" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=46. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 46→60]</t>
+          <t>Skala 60-90 | video: A13 | raw→46→67</t>
         </is>
       </c>
     </row>
@@ -3875,17 +3875,17 @@
       <c r="O41" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P41" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q41" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P41" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q41" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=46. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 46→60]</t>
+          <t>Skala 60-90 | video: A13 | raw→46→67</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       <c r="O4" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q4" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P4" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=48. Komponen lemah: B, C, D, F, G, H, I, J. [min60: 48→60]</t>
+          <t>Skala 60-90 | video: B1 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -4313,17 +4313,17 @@
       <c r="O5" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P5" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=48. Komponen lemah: B, C, D, F, G, H, I, J. [min60: 48→60]</t>
+          <t>Skala 60-90 | video: B1 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -4383,17 +4383,17 @@
       <c r="O6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P6" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q6" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P6" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q6" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=48. Komponen lemah: B, C, D, F, G, H, I, J. [min60: 48→60]</t>
+          <t>Skala 60-90 | video: B1 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -4453,17 +4453,17 @@
       <c r="O7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q7" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P7" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q7" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=48. Komponen lemah: B, C, D, F, G, H, I, J. [min60: 48→60]</t>
+          <t>Skala 60-90 | video: B1 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -4523,17 +4523,17 @@
       <c r="O8" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P8" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q8" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P8" s="41" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q8" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=54. Komponen lemah: C, D, F, G, H, J. [min60: 54→60]</t>
+          <t>Skala 60-90 | video: B2 | raw→49→69</t>
         </is>
       </c>
     </row>
@@ -4593,17 +4593,17 @@
       <c r="O9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P9" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P9" s="41" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q9" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=54. Komponen lemah: C, D, F, G, H, J. [min60: 54→60]</t>
+          <t>Skala 60-90 | video: B2 | raw→49→69</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4663,17 @@
       <c r="O10" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P10" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P10" s="41" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q10" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=54. Komponen lemah: C, D, F, G, H, J. [min60: 54→60]</t>
+          <t>Skala 60-90 | video: B2 | raw→49→69</t>
         </is>
       </c>
     </row>
@@ -4733,17 +4733,17 @@
       <c r="O11" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P11" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q11" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P11" s="41" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q11" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=54. Komponen lemah: C, D, F, G, H, J. [min60: 54→60]</t>
+          <t>Skala 60-90 | video: B2 | raw→49→69</t>
         </is>
       </c>
     </row>
@@ -4803,17 +4803,17 @@
       <c r="O12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P12" s="39" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q12" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P12" s="42" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=82.</t>
+          <t>Skala 60-90 | video: B3 | raw→77→89</t>
         </is>
       </c>
     </row>
@@ -4873,17 +4873,17 @@
       <c r="O13" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P13" s="39" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q13" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P13" s="42" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=82.</t>
+          <t>Skala 60-90 | video: B3 | raw→77→89</t>
         </is>
       </c>
     </row>
@@ -4943,17 +4943,17 @@
       <c r="O14" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P14" s="39" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q14" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P14" s="42" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=82.</t>
+          <t>Skala 60-90 | video: B3 | raw→77→89</t>
         </is>
       </c>
     </row>
@@ -5013,17 +5013,17 @@
       <c r="O15" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="39" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q15" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P15" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q15" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: J.</t>
+          <t>Skala 60-90 | video: B4 | raw→71→85</t>
         </is>
       </c>
     </row>
@@ -5083,17 +5083,17 @@
       <c r="O16" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="39" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q16" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P16" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q16" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: J.</t>
+          <t>Skala 60-90 | video: B4 | raw→71→85</t>
         </is>
       </c>
     </row>
@@ -5153,17 +5153,17 @@
       <c r="O17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P17" s="39" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q17" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P17" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q17" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: J.</t>
+          <t>Skala 60-90 | video: B4 | raw→71→85</t>
         </is>
       </c>
     </row>
@@ -5223,17 +5223,17 @@
       <c r="O18" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P18" s="39" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q18" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P18" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q18" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77. Komponen lemah: J.</t>
+          <t>Skala 60-90 | video: B4 | raw→71→85</t>
         </is>
       </c>
     </row>
@@ -5293,17 +5293,17 @@
       <c r="O19" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P19" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q19" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P19" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: D, E.</t>
+          <t>Skala 60-90 | video: B5 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -5363,17 +5363,17 @@
       <c r="O20" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P20" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q20" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P20" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q20" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: D, E.</t>
+          <t>Skala 60-90 | video: B5 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -5433,17 +5433,17 @@
       <c r="O21" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q21" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P21" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q21" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: D, E.</t>
+          <t>Skala 60-90 | video: B5 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -5503,17 +5503,17 @@
       <c r="O22" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P22" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q22" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P22" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q22" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: D, E.</t>
+          <t>Skala 60-90 | video: B5 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -5573,17 +5573,17 @@
       <c r="O23" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q23" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P23" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q23" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=47. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 47→60]</t>
+          <t>Skala 60-90 | video: B6 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -5643,17 +5643,17 @@
       <c r="O24" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q24" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P24" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q24" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=47. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 47→60]</t>
+          <t>Skala 60-90 | video: B6 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -5713,17 +5713,17 @@
       <c r="O25" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P25" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q25" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P25" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q25" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=47. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 47→60]</t>
+          <t>Skala 60-90 | video: B6 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -5783,17 +5783,17 @@
       <c r="O26" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P26" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q26" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P26" s="41" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q26" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=47. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 47→60]</t>
+          <t>Skala 60-90 | video: B6 | raw→47→67</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="R27" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: B7 | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="R28" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: B7 | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="R29" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: B7 | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="R30" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: B7 | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -6041,17 +6041,17 @@
       <c r="O31" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P31" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q31" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P31" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q31" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: H.</t>
+          <t>Skala 60-90 | video: B8 | raw→65→80</t>
         </is>
       </c>
     </row>
@@ -6111,17 +6111,17 @@
       <c r="O32" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P32" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q32" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P32" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q32" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: H.</t>
+          <t>Skala 60-90 | video: B8 | raw→65→80</t>
         </is>
       </c>
     </row>
@@ -6181,17 +6181,17 @@
       <c r="O33" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P33" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q33" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P33" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q33" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: H.</t>
+          <t>Skala 60-90 | video: B8 | raw→65→80</t>
         </is>
       </c>
     </row>
@@ -6251,17 +6251,17 @@
       <c r="O34" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P34" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q34" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P34" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: F, J.</t>
+          <t>Skala 60-90 | video: B9 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -6321,17 +6321,17 @@
       <c r="O35" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P35" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q35" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P35" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q35" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: F, J.</t>
+          <t>Skala 60-90 | video: B9 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -6391,17 +6391,17 @@
       <c r="O36" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P36" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q36" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P36" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: F, J.</t>
+          <t>Skala 60-90 | video: B9 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -6461,17 +6461,17 @@
       <c r="O37" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P37" s="41" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q37" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P37" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=69. Komponen lemah: F, J.</t>
+          <t>Skala 60-90 | video: B9 | raw→61→78</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
         <v>7</v>
       </c>
       <c r="P38" s="39" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q38" s="39" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=79.</t>
+          <t>Skala 60-90 | video: B10 | raw→67→82</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
         <v>7</v>
       </c>
       <c r="P39" s="39" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q39" s="39" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=79.</t>
+          <t>Skala 60-90 | video: B10 | raw→67→82</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
         <v>7</v>
       </c>
       <c r="P40" s="39" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q40" s="39" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=79.</t>
+          <t>Skala 60-90 | video: B10 | raw→67→82</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
         <v>7</v>
       </c>
       <c r="P41" s="39" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q41" s="39" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=79.</t>
+          <t>Skala 60-90 | video: B10 | raw→67→82</t>
         </is>
       </c>
     </row>
@@ -6811,17 +6811,17 @@
       <c r="O42" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P42" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q42" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P42" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q42" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: B11 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -7263,17 +7263,17 @@
       <c r="O6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P6" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q6" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P6" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: C3 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -7333,17 +7333,17 @@
       <c r="O7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q7" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P7" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: C3 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -7403,17 +7403,17 @@
       <c r="O8" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P8" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q8" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P8" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: C3 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -7473,17 +7473,17 @@
       <c r="O9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P9" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P9" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: C3 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -7543,17 +7543,17 @@
       <c r="O10" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P10" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P10" s="41" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q10" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=55. Komponen lemah: C, D, E, F, G, J. [min60: 55→60]</t>
+          <t>Skala 60-90 | video: C4 | raw→52→71</t>
         </is>
       </c>
     </row>
@@ -7613,17 +7613,17 @@
       <c r="O11" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P11" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q11" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P11" s="41" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=55. Komponen lemah: C, D, E, F, G, J. [min60: 55→60]</t>
+          <t>Skala 60-90 | video: C4 | raw→52→71</t>
         </is>
       </c>
     </row>
@@ -7683,17 +7683,17 @@
       <c r="O12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P12" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q12" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P12" s="41" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q12" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=55. Komponen lemah: C, D, E, F, G, J. [min60: 55→60]</t>
+          <t>Skala 60-90 | video: C4 | raw→52→71</t>
         </is>
       </c>
     </row>
@@ -7753,17 +7753,17 @@
       <c r="O13" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P13" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q13" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P13" s="41" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q13" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=55. Komponen lemah: C, D, E, F, G, J. [min60: 55→60]</t>
+          <t>Skala 60-90 | video: C4 | raw→52→71</t>
         </is>
       </c>
     </row>
@@ -7823,17 +7823,17 @@
       <c r="O14" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P14" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q14" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P14" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q14" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=56. Komponen lemah: B, C, D, E, F, G, J. [min60: 56→60]</t>
+          <t>Skala 60-90 | video: C5 | raw→53→72</t>
         </is>
       </c>
     </row>
@@ -7893,17 +7893,17 @@
       <c r="O15" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q15" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P15" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=56. Komponen lemah: B, C, D, E, F, G, J. [min60: 56→60]</t>
+          <t>Skala 60-90 | video: C5 | raw→53→72</t>
         </is>
       </c>
     </row>
@@ -7963,17 +7963,17 @@
       <c r="O16" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q16" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P16" s="41" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q16" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=56. Komponen lemah: B, C, D, E, F, G, J. [min60: 56→60]</t>
+          <t>Skala 60-90 | video: C5 | raw→53→72</t>
         </is>
       </c>
     </row>
@@ -8033,17 +8033,17 @@
       <c r="O17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P17" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q17" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P17" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q17" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: C, D, F, J.</t>
+          <t>Skala 60-90 | video: C6 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -8103,17 +8103,17 @@
       <c r="O18" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P18" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q18" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P18" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q18" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: C, D, F, J.</t>
+          <t>Skala 60-90 | video: C6 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -8173,17 +8173,17 @@
       <c r="O19" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q19" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P19" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: C, D, F, J.</t>
+          <t>Skala 60-90 | video: C6 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -8243,17 +8243,17 @@
       <c r="O20" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P20" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q20" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P20" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q20" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: C, D, F, J.</t>
+          <t>Skala 60-90 | video: C6 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -8313,17 +8313,17 @@
       <c r="O21" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P21" s="40" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q21" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P21" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q21" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=63. Komponen lemah: F, G, H, J.</t>
+          <t>Skala 60-90 | video: C7 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -8383,17 +8383,17 @@
       <c r="O22" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="40" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q22" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P22" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q22" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=63. Komponen lemah: F, G, H, J.</t>
+          <t>Skala 60-90 | video: C7 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -8453,17 +8453,17 @@
       <c r="O23" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="40" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q23" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P23" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q23" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=63. Komponen lemah: F, G, H, J.</t>
+          <t>Skala 60-90 | video: C7 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -8523,17 +8523,17 @@
       <c r="O24" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="40" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q24" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P24" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q24" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=63. Komponen lemah: F, G, H, J.</t>
+          <t>Skala 60-90 | video: C7 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=38. Komponen lemah: A, C, D, E, F, G, H, I, J. [min60: 38→60]</t>
+          <t>Skala 60-90 | video: C8 | raw→37→60</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=38. Komponen lemah: A, C, D, E, F, G, H, I, J. [min60: 38→60]</t>
+          <t>Skala 60-90 | video: C8 | raw→37→60</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=38. Komponen lemah: A, C, D, E, F, G, H, I, J. [min60: 38→60]</t>
+          <t>Skala 60-90 | video: C8 | raw→37→60</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=38. Komponen lemah: A, C, D, E, F, G, H, I, J. [min60: 38→60]</t>
+          <t>Skala 60-90 | video: C8 | raw→37→60</t>
         </is>
       </c>
     </row>
@@ -8873,17 +8873,17 @@
       <c r="O29" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P29" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q29" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P29" s="39" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q29" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: B, I, J.</t>
+          <t>Skala 60-90 | video: C9 | raw→59→76</t>
         </is>
       </c>
     </row>
@@ -8943,17 +8943,17 @@
       <c r="O30" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P30" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q30" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P30" s="39" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q30" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: B, I, J.</t>
+          <t>Skala 60-90 | video: C9 | raw→59→76</t>
         </is>
       </c>
     </row>
@@ -9013,17 +9013,17 @@
       <c r="O31" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P31" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q31" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P31" s="39" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q31" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: B, I, J.</t>
+          <t>Skala 60-90 | video: C9 | raw→59→76</t>
         </is>
       </c>
     </row>
@@ -9083,17 +9083,17 @@
       <c r="O32" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P32" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q32" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P32" s="39" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q32" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: B, I, J.</t>
+          <t>Skala 60-90 | video: C9 | raw→59→76</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="R33" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="R34" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="R35" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="R36" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -9337,17 +9337,17 @@
       <c r="O37" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P37" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q37" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P37" s="41" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q37" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=45. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 45→60]</t>
+          <t>Skala 60-90 | video: C11 | raw→45→66</t>
         </is>
       </c>
     </row>
@@ -9407,17 +9407,17 @@
       <c r="O38" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P38" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q38" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P38" s="41" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q38" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=45. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 45→60]</t>
+          <t>Skala 60-90 | video: C11 | raw→45→66</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
         <v>8</v>
       </c>
       <c r="P39" s="39" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q39" s="39" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77.</t>
+          <t>Skala 60-90 | video: C12 | raw→66→81</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
         <v>8</v>
       </c>
       <c r="P40" s="39" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q40" s="39" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77.</t>
+          <t>Skala 60-90 | video: C12 | raw→66→81</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9618,7 @@
         <v>8</v>
       </c>
       <c r="P41" s="39" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q41" s="39" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=77.</t>
+          <t>Skala 60-90 | video: C12 | raw→66→81</t>
         </is>
       </c>
     </row>
@@ -9982,17 +9982,17 @@
       <c r="O4" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="41" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P4" s="39" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=70. Komponen lemah: J.</t>
+          <t>Skala 60-90 | video: D1 | raw→63→79</t>
         </is>
       </c>
     </row>
@@ -10052,17 +10052,17 @@
       <c r="O5" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="41" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q5" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P5" s="39" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q5" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=70. Komponen lemah: J.</t>
+          <t>Skala 60-90 | video: D1 | raw→63→79</t>
         </is>
       </c>
     </row>
@@ -10122,17 +10122,17 @@
       <c r="O6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P6" s="41" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q6" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P6" s="39" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q6" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=70. Komponen lemah: J.</t>
+          <t>Skala 60-90 | video: D1 | raw→63→79</t>
         </is>
       </c>
     </row>
@@ -10192,17 +10192,17 @@
       <c r="O7" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P7" s="39" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q7" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P7" s="42" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q7" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R7" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=82.</t>
+          <t>Skala 60-90 | video: D2 | raw→74→87</t>
         </is>
       </c>
     </row>
@@ -10262,17 +10262,17 @@
       <c r="O8" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P8" s="39" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q8" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P8" s="42" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=82.</t>
+          <t>Skala 60-90 | video: D2 | raw→74→87</t>
         </is>
       </c>
     </row>
@@ -10332,17 +10332,17 @@
       <c r="O9" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="P9" s="39" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q9" s="39" t="inlineStr">
-        <is>
-          <t>AB</t>
+      <c r="P9" s="42" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=82.</t>
+          <t>Skala 60-90 | video: D2 | raw→74→87</t>
         </is>
       </c>
     </row>
@@ -10402,17 +10402,17 @@
       <c r="O10" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P10" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q10" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P10" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q10" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, D, F, I, J.</t>
+          <t>Skala 60-90 | video: D3 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -10472,17 +10472,17 @@
       <c r="O11" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P11" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q11" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P11" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q11" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, D, F, I, J.</t>
+          <t>Skala 60-90 | video: D3 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -10542,17 +10542,17 @@
       <c r="O12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P12" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q12" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P12" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q12" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, D, F, I, J.</t>
+          <t>Skala 60-90 | video: D3 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -10612,17 +10612,17 @@
       <c r="O13" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P13" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q13" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P13" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q13" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, D, F, I, J.</t>
+          <t>Skala 60-90 | video: D3 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -10726,17 +10726,17 @@
       <c r="O15" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q15" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P15" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q15" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: G, J.</t>
+          <t>Skala 60-90 | video: D5 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -10796,17 +10796,17 @@
       <c r="O16" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q16" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P16" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q16" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: G, J.</t>
+          <t>Skala 60-90 | video: D5 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -10866,17 +10866,17 @@
       <c r="O17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P17" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q17" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P17" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q17" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: G, J.</t>
+          <t>Skala 60-90 | video: D5 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -10936,17 +10936,17 @@
       <c r="O18" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P18" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q18" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P18" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q18" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=66. Komponen lemah: G, J.</t>
+          <t>Skala 60-90 | video: D5 | raw→58→75</t>
         </is>
       </c>
     </row>
@@ -11006,17 +11006,17 @@
       <c r="O19" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q19" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P19" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q19" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: D6 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -11076,17 +11076,17 @@
       <c r="O20" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P20" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q20" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P20" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: D6 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -11146,17 +11146,17 @@
       <c r="O21" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P21" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q21" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P21" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: D6 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -11216,17 +11216,17 @@
       <c r="O22" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q22" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P22" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q22" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: D6 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -11286,17 +11286,17 @@
       <c r="O23" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P23" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q23" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P23" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q23" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: F.</t>
+          <t>Skala 60-90 | video: D7 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -11356,17 +11356,17 @@
       <c r="O24" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P24" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q24" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P24" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q24" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: F.</t>
+          <t>Skala 60-90 | video: D7 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -11426,17 +11426,17 @@
       <c r="O25" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P25" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q25" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P25" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q25" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: F.</t>
+          <t>Skala 60-90 | video: D7 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -11496,17 +11496,17 @@
       <c r="O26" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="P26" s="41" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q26" s="41" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="P26" s="39" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q26" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=72. Komponen lemah: F.</t>
+          <t>Skala 60-90 | video: D7 | raw→62→78</t>
         </is>
       </c>
     </row>
@@ -11567,7 +11567,7 @@
         <v>8</v>
       </c>
       <c r="P27" s="42" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q27" s="42" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=85.</t>
+          <t>Skala 60-90 | video: D8 | raw→78→90</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
         <v>8</v>
       </c>
       <c r="P28" s="42" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q28" s="42" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=85.</t>
+          <t>Skala 60-90 | video: D8 | raw→78→90</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11707,7 @@
         <v>8</v>
       </c>
       <c r="P29" s="42" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="42" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=85.</t>
+          <t>Skala 60-90 | video: D8 | raw→78→90</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
         <v>8</v>
       </c>
       <c r="P30" s="42" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q30" s="42" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=85.</t>
+          <t>Skala 60-90 | video: D8 | raw→78→90</t>
         </is>
       </c>
     </row>
@@ -11890,17 +11890,17 @@
       <c r="O32" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P32" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q32" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P32" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q32" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, E, F, J.</t>
+          <t>Skala 60-90 | video: D10 | raw→57→75</t>
         </is>
       </c>
     </row>
@@ -11960,17 +11960,17 @@
       <c r="O33" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q33" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P33" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q33" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, E, F, J.</t>
+          <t>Skala 60-90 | video: D10 | raw→57→75</t>
         </is>
       </c>
     </row>
@@ -12030,17 +12030,17 @@
       <c r="O34" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P34" s="40" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q34" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P34" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q34" s="39" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=62. Komponen lemah: C, E, F, J.</t>
+          <t>Skala 60-90 | video: D10 | raw→57→75</t>
         </is>
       </c>
     </row>
@@ -12434,17 +12434,17 @@
       <c r="O5" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P5" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: E2 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -12504,17 +12504,17 @@
       <c r="O6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P6" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q6" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P6" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: E2 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -12574,17 +12574,17 @@
       <c r="O7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q7" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P7" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R7" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: E2 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -12644,17 +12644,17 @@
       <c r="O8" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P8" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q8" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P8" s="41" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=44. Komponen lemah: B, C, D, E, F, G, H, I, J. [min60: 44→60]</t>
+          <t>Skala 60-90 | video: E2 | raw→44→65</t>
         </is>
       </c>
     </row>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="R9" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="R10" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="R11" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="R12" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -12902,17 +12902,17 @@
       <c r="O13" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P13" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q13" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P13" s="41" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q13" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=52. Komponen lemah: C, D, F, G, H, I, J. [min60: 52→60]</t>
+          <t>Skala 60-90 | video: E4 | raw→49→69</t>
         </is>
       </c>
     </row>
@@ -12972,17 +12972,17 @@
       <c r="O14" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P14" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q14" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P14" s="41" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=52. Komponen lemah: C, D, F, G, H, I, J. [min60: 52→60]</t>
+          <t>Skala 60-90 | video: E4 | raw→49→69</t>
         </is>
       </c>
     </row>
@@ -13042,17 +13042,17 @@
       <c r="O15" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q15" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P15" s="41" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q15" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=52. Komponen lemah: C, D, F, G, H, I, J. [min60: 52→60]</t>
+          <t>Skala 60-90 | video: E4 | raw→49→69</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="R16" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="R17" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="R18" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="R19" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="R20" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="R21" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="R22" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="R23" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="R24" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="R25" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="R26" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="R27" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="R28" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="R29" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="R30" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="R31" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -13864,17 +13864,17 @@
       <c r="O32" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P32" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q32" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P32" s="41" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=49. Komponen lemah: C, D, E, F, G, H, I, J. [min60: 49→60]</t>
+          <t>Skala 60-90 | video: E9 | raw→48→68</t>
         </is>
       </c>
     </row>
@@ -13934,17 +13934,17 @@
       <c r="O33" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q33" s="40" t="inlineStr">
-        <is>
-          <t>BC</t>
+      <c r="P33" s="41" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q33" s="41" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>Sumber: deskripsi YouTube. Total=49. Komponen lemah: C, D, E, F, G, H, I, J. [min60: 49→60]</t>
+          <t>Skala 60-90 | video: E9 | raw→48→68</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="R34" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="R35" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="R36" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -14136,7 +14136,7 @@
       </c>
       <c r="R37" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="R38" s="35" t="inlineStr">
         <is>
-          <t>Video tidak dapat diakses (404/private)</t>
+          <t>Skala 60-90 | video: N/A | raw→0→60</t>
         </is>
       </c>
     </row>
